--- a/consent_forms/042_medical_consent_and_indemnity_form--consent_forms.xlsx
+++ b/consent_forms/042_medical_consent_and_indemnity_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -845,12 +845,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -878,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'date',_'label':_'today'}</t>
+          <t>today</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'date', 'label': 'today'}</t>
+          <t>today</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'later',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'later', 'label': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'notary',_'label':_'notarized'}</t>
+          <t>notarized</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'notary', 'label': 'notarized'}</t>
+          <t>notarized</t>
         </is>
       </c>
     </row>
@@ -1031,29 +1031,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'non_notarized',_'label':_'non-notarized'}</t>
+          <t>non-notarized</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'non_notarized', 'label': 'non-notarized'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>signature_notary_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>{'value':_'notarized',_'label':_'notarized'}</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>{'value': 'notarized', 'label': 'notarized'}</t>
+          <t>non-notarized</t>
         </is>
       </c>
     </row>
